--- a/docs/KARTOCHKI-SAYTA.xlsx
+++ b/docs/KARTOCHKI-SAYTA.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Препараты" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Семена" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3473,4 +3474,1292 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Культура · Тип</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Урожайность</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Спелость</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вег. период</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Оригинатор</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Новосёл CL</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Рапс яровой · гибрид F1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>12,5–15 ц/га (+11% к стандарту)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>среднеранний</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>100 дней</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>масличность 43–46%, выход масла 6,6–9,4 ц/га</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Высокоурожайный и высокомасличный среднеранний гибрид 00 типа, безэруковый, низкоглюкозинолатный. Под систему Clearfield. Устойчив к полеганию и осыпанию, отзывчив на удобрения</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>novosel-cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ampir 10 Express</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник · гибрид F1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>потенциал 5,6 т/га</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>масличность 50–53%, масса 1000 семян 46 г</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Гибрид нового поколения под технологию ExpressSun. Высокая устойчивость к фомопсису, склеротинии и ЛМР</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ampir-10-express</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Ampir 25 Express</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник · гибрид F1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>потенциал 5,6 т/га</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>масличность 50–53%, масса 1000 семян 46 г</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Гибрид нового поколения под технологию ExpressSun. Высокая устойчивость к фомопсису, склеротинии и ЛМР</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>ampir-25-express</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Скипетр</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница озимая · ЭС</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>средняя 32,5 ц/га, максимальная 71,3 ц/га</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>297–338 дней</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ценная · белок 12,3–15,6%, клейковина 22,1–30,8%, масса 1000 зёрен 38–49 г</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>КФХ «Приволье-1», Полетаев Г.М., ООО «ЭкоНива-Семена»</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Среднеспелый, низкорослый сорт мягкой озимой пшеницы, устойчив к полеганию</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>skipetr</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Собербаш</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница озимая · ЭС, РС 1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>средняя 68,1 ц/га (ЦЧР), максимальная 119 ц/га</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>216–308 дней</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ценная · белок 15–17%, клейковина до 33% · масса 1000 зёрен 42–51 г</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «НЦЗ им. П.П. Лукьяненко»</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Среднеспелый, среднерослый сорт мягкой озимой пшеницы, устойчив к полеганию. Для хлебопекарного производства</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>soberbash</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Льговская 4</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница озимая · ЭС</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>максимальная 105 ц/га</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>284–316 дней</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ценная · белок около 15,6% · масса 1000 зёрен 48,5 г</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Льговская опытно-селекционная станция</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Короткостебельный, высокоадаптивный сорт интенсивного типа с повышенной зимо- и морозостойкостью. Устойчив к полеганию</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>lgovskaya-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Прииртышская 2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница озимая · ЭС</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>средняя 59,4 ц/га, максимальная 69,0 ц/га</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>335 суток</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ценная · белок 14,0%, клейковина 28,2%, масса 1000 зёрен 43,3 г</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «Омский АНЦ»</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Озимая мягкая пшеница сибирской селекции. Устойчива к осыпанию, полеганию и засухе, зимостойкость 73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>priirtyshskaya-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>КВС Аквилон</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая · РС 1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>потенциал 90 ц/га, по ГСИ 54,2 ц/га</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>76–84 дня</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>ценная (1–2 класс) · белок 14–16%, клейковина 28–30%, масса 1000 зёрен 32–37 г, натура 750–820 г/л</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>KWS</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Сбалансированное сочетание высокой урожайности, устойчивости к болезням и качества зерна</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>kvs-akvilon</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>КВС Буран</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая · РС 1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>потенциал 95 ц/га, по ГСИ 67,0 ц/га</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77–86 дней</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>белок 13,3%, клейковина 28–30%, масса 1000 зёрен 39–45 г, натура 785–805 г/л, стекловидность 81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>KWS</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Высокая урожайность при сбалансированной устойчивости и качестве зерна. Мощный колос и высокая масса 1000 зёрен</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>kvs-buran</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Гонец</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая · ЭС</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>средняя 38,0 ц/га (Западная Сибирь), максимальная 84,2 ц/га</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>среднепоздний</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81–93 дня</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ценная · масса 1000 зёрен 35–48 г</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «ФАНЦА»</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Среднепоздний, низкорослый сорт мягкой яровой пшеницы. Устойчив к полеганию, пыльной головне и бурой ржавчине</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>gonets</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Юнион</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая · ЭС</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>средняя 35,1 ц/га (Западная Сибирь), 42,3 ц/га (Восточная Сибирь), максимальная 98,0 ц/га</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82–97 дней</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ценная · белок 15–16%, клейковина 25–29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ ФАНЦА (Барнаул)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Среднеспелый сорт мягкой яровой пшеницы алтайской селекции, ценная по качеству</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>yunion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Алтайский 22</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Ячмень яровой · ЭС</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>средняя 34,6 ц/га (Западная Сибирь), максимальная 59,6 ц/га</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>74–76 дней</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>зернофуражный · белок 9–15%, крахмал 56,7–64,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ ФАНЦА (Барнаул)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Среднеспелый ячмень алтайской селекции (ФАНЦА), включён в Госреестр в 2025 году. Засухоустойчив, устойчив к полеганию</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>altayskiy-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>КВС Джесси</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Ячмень яровой · РС 1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>потенциал до 110 ц/га</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>раннеспелый</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>74–82 дня</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>пивоваренный · белок 10–11%, масса 1000 зёрен 41–53 г</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>KWS</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Среднеранний сорт двойного назначения с высоким потенциалом урожайности и превосходными пивоваренными характеристиками</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>kvs-dzhessi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>КВС Хоббс</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Ячмень яровой · РС 1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>потенциал 120 ц/га, максимальная по ГСИ 108 ц/га</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>76–88 дней</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>пивоваренный · белок 10–11%, масса 1000 зёрен 47–55 г</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>KWS</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Пивоваренный ячмень, отлично подходящий для производства светлых типов солода</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>kvs-hobbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Золотистая</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Соя · ЭС</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>средняя 17,0 ц/га, максимальная 38,1 ц/га</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>среднеранний</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>92–99 дней</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>белок 30,0–39,5%, жир 16,5–23,9%, масса 1000 семян 123–176 г</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «Омский АНЦ»</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Растение индетерминантного типа, средней высоты. Устойчив к засухе</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>zolotistaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Сибириада</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Соя · ЭС</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>средняя 14,3 ц/га, максимальная 39,7 ц/га</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>раннеспелый</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>97 дней</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>белок 35,2%, жир 20,25%, масса 1000 семян 131,6 г</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «Омский АНЦ»</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Раннеспелый сорт. Рекомендован для Новосибирской, Омской областей и Красноярского края. Устойчив к засухе</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>sibiriada</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Сибириада 20</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Соя · ЭС</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>средняя 35,2 ц/га, максимальная 44,6 ц/га</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>скороспелый</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88–108 суток</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>белок 37,7%, жир 18,76%, масса 1000 семян 160–209 г</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «Омский АНЦ»</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Скороспелый сорт с высоким прикреплением нижних бобов и повышенной масличностью. Бобы устойчивы к растрескиванию</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>sibiriada-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Сентябринка</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Соя · ЭС</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>средняя 20,8 ц/га, максимальная 31 ц/га</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>раннеспелый</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>87–107 дней</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>белок 40,92%, жир 18,68%, масса 1000 семян 162 г</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>ФНЦ «ВНИИ сои»</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Раннеспелый, среднерослый сорт индетерминантного типа, семена жёлто-зелёные</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>sentyabrinka</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Топаз</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Соя · ЭС</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>средняя 16,7 ц/га, максимальная 24,3 ц/га</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>очень ранний — ранний</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>89–102 дня</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>белок 39,93%, жир 20,50%, масса 1000 семян 172,3 г</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>ФНЦ «ВНИИ сои»</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Индетерминантный, низко-среднерослый сорт, семена жёлтые</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>topaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Черемшанка</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Соя · ЭС</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>потенциальная 39,3 ц/га</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>ультраранний</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>85–90 дней</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>белок 39,6%, жир 18,9%, масса 1000 семян 131–172 г</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «Омский АНЦ»</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Скороспелый сорт, устойчив к бактериозу. Высота прикрепления нижнего боба 14,5 см</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>cheremshanka</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>КВС Багу</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Горох посевной · РС 1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>по ГСИ 46–52 ц/га, максимальная 55 ц/га</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>67–85 дней</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>белок 23,3–24,8%, масса 1000 зёрен 175–230 г</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>KWS</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Среднерослый сорт с оптимальным расположением бобов к уборке. Лидирующий горох KWS в мире</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>kvs-bagu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Бонус 2</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Горох посевной · ЭС</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2,66–4,82 т/га в конкурсном испытании, максимальная 4,82 т/га</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>70–80 суток</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>белок 23,1–26,8%, масса 1000 семян 245–270 г, выравненность 93,6%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ФГБНУ «Омский АНЦ»</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Усатый сорт с укороченным стеблем и ограниченным типом роста. Устойчив к полеганию, семена не осыпаются, бобы формируются в верхней части растения — убирается прямым комбайнированием</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>bonus-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Даша</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Гречиха · ЭС</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>средняя 20,0 ц/га (Западная Сибирь), максимальная 37,5 ц/га</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>74–105 дней</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>технологические и кулинарные качества высокие · масса 1000 зёрен 25–38 г</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>ФНЦ ЗБК, Орловский ГАУ</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Детерминантный тип роста. Устойчивость к полеганию, осыпанию и засухе выше средней. Слабо поражается болезнями</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>dasha</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Диана</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Гречиха · ЭС</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>средняя 19,7 ц/га (Восточная Сибирь), максимальная 43,0 ц/га</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>среднеспелый</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>80–101 день</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ценная по качеству · масса 1000 зёрен 28–38 г</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ФНЦ ЗБК</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Ценный по качеству зерна. Технологические и кулинарные качества высокие</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>diana</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Инноватор</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Картофель · ЭС</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>средняя 155–329 ц/га, максимальная 344 ц/га</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>среднеранний</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>75–85 суток</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>крахмал 12–15%, товарность 82–96%, масса клубня 83–147 г, лёжкость 95%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>HZPC Holland B.V., ФИЦ картофеля им. А.Г. Лорха</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Столового назначения, для жарки во фритюре. Пригоден для длительного хранения</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>innovator</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/KARTOCHKI-SAYTA.xlsx
+++ b/docs/KARTOCHKI-SAYTA.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>от 645,7 ₽/л</t>
+          <t>от 585 ₽/л</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>от 724,5 ₽/л</t>
+          <t>от 700 ₽/л</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>от 651 ₽/л</t>
+          <t>от 595 ₽/л</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>от 651 ₽/л</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>от 409,5 ₽/л</t>
+          <t>от 315 ₽/л</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>от 577,5 ₽/л</t>
+          <t>от 535 ₽/л</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>от 332,5 ₽/л</t>
+          <t>от 315 ₽/л</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>от 490 ₽/л</t>
+          <t>от 450 ₽/л</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>от 760 ₽/л</t>
+          <t>от 635 ₽/л</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>от 728 ₽/л</t>
+          <t>от 500 ₽/л</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>от 430 ₽/л</t>
+          <t>от 400 ₽/л</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>от 465 ₽/л</t>
+          <t>от 545 ₽/л</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>от 1290 ₽/л</t>
+          <t>от 1470 ₽/л</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>от 650 ₽/л</t>
+          <t>от 685 ₽/л</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>от 653 ₽/л</t>
+          <t>от 670 ₽/л</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>от 520 ₽/л</t>
+          <t>от 455 ₽/л</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>от 605 ₽/л</t>
+          <t>от 510 ₽/л</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>от 1290 ₽/л</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>от 695 ₽/л</t>
+          <t>от 800 ₽/л</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>от 1020 ₽/л</t>
+          <t>от 1245 ₽/л</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">

--- a/docs/KARTOCHKI-SAYTA.xlsx
+++ b/docs/KARTOCHKI-SAYTA.xlsx
@@ -3230,7 +3230,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>от 220 ₽/л</t>
+          <t>от 220 ₽/кг</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>от 1350 ₽/л</t>
+          <t>от 1350 ₽/кг</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>от 426 ₽/л</t>
+          <t>от 426 ₽/кг</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
